--- a/python/output/TRADE.xlsx
+++ b/python/output/TRADE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D554"/>
+  <dimension ref="A1:D712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9243,6 +9243,2518 @@
         <v>50.7596590804177</v>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" s="1" t="n">
+        <v>1866</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D555" t="n">
+        <v>61.5262136695806</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="n">
+        <v>1870</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D556" t="n">
+        <v>182.909355066597</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="n">
+        <v>1871</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D557" t="n">
+        <v>33.078689567466</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="n">
+        <v>1875</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D558" t="n">
+        <v>40.2022359390595</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="n">
+        <v>1876</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D559" t="n">
+        <v>111.032932124165</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="n">
+        <v>1879</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D560" t="n">
+        <v>177.381892440073</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="n">
+        <v>1882</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>BGD</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D561" t="n">
+        <v>27.7240047036631</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="n">
+        <v>1883</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D562" t="n">
+        <v>121.214088263823</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="n">
+        <v>1887</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D563" t="n">
+        <v>136.014167877476</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D564" t="n">
+        <v>37.6563307592575</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="n">
+        <v>1893</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D565" t="n">
+        <v>147.123112375318</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="n">
+        <v>1897</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D566" t="n">
+        <v>62.2468367159421</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="n">
+        <v>1899</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D567" t="n">
+        <v>130.016261288489</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D568" t="n">
+        <v>64.8774063237834</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D569" t="n">
+        <v>36.5206911762676</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D570" t="n">
+        <v>45.1140327762435</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D571" t="n">
+        <v>36.7308347188558</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D572" t="n">
+        <v>75.38705238607319</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D573" t="n">
+        <v>40.0591463936128</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="n">
+        <v>1910</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D574" t="n">
+        <v>70.78164230270851</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>1915</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>CYP</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D575" t="n">
+        <v>176.82773681987</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>1916</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D576" t="n">
+        <v>137.378116302868</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>1917</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D577" t="n">
+        <v>79.9195348609851</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>DNK</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D578" t="n">
+        <v>112.321472697291</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>1929</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D579" t="n">
+        <v>29.8569734808122</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>1932</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D580" t="n">
+        <v>66.52458894319101</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>1933</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D581" t="n">
+        <v>160.471922305927</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>1937</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D582" t="n">
+        <v>79.7892781913782</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>1939</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D583" t="n">
+        <v>63.788482630872</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D584" t="n">
+        <v>58.53838629291</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="n">
+        <v>1951</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D585" t="n">
+        <v>88.0126654490379</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D586" t="n">
+        <v>402.459681454463</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>HRV</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D587" t="n">
+        <v>102.328697150799</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D588" t="n">
+        <v>159.187527332834</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D589" t="n">
+        <v>40.2047582749671</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D590" t="n">
+        <v>45.4230887840446</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D591" t="n">
+        <v>231.032350863586</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>ISL</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D592" t="n">
+        <v>76.2317249850944</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D593" t="n">
+        <v>54.9016842006986</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D594" t="n">
+        <v>60.3019776202798</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>JOR</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D595" t="n">
+        <v>80.3328699444404</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D596" t="n">
+        <v>36.7384462280698</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D597" t="n">
+        <v>58.6686085779207</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>KHM</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D598" t="n">
+        <v>146.179846509715</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D599" t="n">
+        <v>75.3063047610912</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>LAO</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>LTU</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D601" t="n">
+        <v>154.80672767597</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D602" t="n">
+        <v>397.506180867971</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>LVA</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D603" t="n">
+        <v>136.796615414819</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D604" t="n">
+        <v>75.52341717565059</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D605" t="n">
+        <v>83.0692976357895</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>MLT</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D606" t="n">
+        <v>220.165634087757</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>MMR</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D608" t="n">
+        <v>134.035994690727</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>NLD</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D610" t="n">
+        <v>163.154842689698</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D611" t="n">
+        <v>71.2227137759599</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D612" t="n">
+        <v>48.5412477650846</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="n">
+        <v>2046</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D613" t="n">
+        <v>27.0304204125548</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D614" t="n">
+        <v>55.427249365522</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="n">
+        <v>2049</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D615" t="n">
+        <v>63.4846098136712</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="n">
+        <v>2052</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D616" t="n">
+        <v>110.874283021945</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="n">
+        <v>2056</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D617" t="n">
+        <v>85.8735452148975</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="n">
+        <v>2063</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D618" t="n">
+        <v>87.07119654601451</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="n">
+        <v>2064</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D619" t="n">
+        <v>50.5861954621752</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="n">
+        <v>2067</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D620" t="n">
+        <v>50.8839263398787</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="n">
+        <v>2069</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D621" t="n">
+        <v>69.3759939883832</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="n">
+        <v>2070</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D622" t="n">
+        <v>329.161383683762</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="n">
+        <v>2081</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="n">
+        <v>2083</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D624" t="n">
+        <v>181.97948448512</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="n">
+        <v>2084</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>SVN</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D625" t="n">
+        <v>161.788727511439</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="n">
+        <v>2085</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D626" t="n">
+        <v>91.11023744130421</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="n">
+        <v>2095</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D627" t="n">
+        <v>117.252944620852</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D628" t="n">
+        <v>93.63341406640789</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="n">
+        <v>2106</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D629" t="n">
+        <v>69.6088976086437</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="n">
+        <v>2110</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D630" t="n">
+        <v>82.69796136345001</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="n">
+        <v>2113</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D631" t="n">
+        <v>25.6095576621932</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="n">
+        <v>2119</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D632" t="n">
+        <v>186.675832836814</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="n">
+        <v>2125</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D633" t="n">
+        <v>56.1647136277546</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="n">
+        <v>2132</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D634" t="n">
+        <v>55.2547732713835</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="n">
+        <v>2136</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D635" t="n">
+        <v>185.741660982819</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="n">
+        <v>2137</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D636" t="n">
+        <v>31.5801792606256</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="n">
+        <v>2141</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D637" t="n">
+        <v>45.6946418805752</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="n">
+        <v>2142</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D638" t="n">
+        <v>123.579578652902</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="n">
+        <v>2145</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D639" t="n">
+        <v>191.179031303786</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="n">
+        <v>2148</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>BGD</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D640" t="n">
+        <v>33.7799672705735</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="n">
+        <v>2149</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D641" t="n">
+        <v>138.844877241238</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="n">
+        <v>2153</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D642" t="n">
+        <v>120.024207576094</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="n">
+        <v>2157</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D643" t="n">
+        <v>38.8160659764321</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="n">
+        <v>2159</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D644" t="n">
+        <v>146.973965879597</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="n">
+        <v>2163</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D645" t="n">
+        <v>67.3176215563989</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="n">
+        <v>2165</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D646" t="n">
+        <v>138.500698753519</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="n">
+        <v>2167</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D647" t="n">
+        <v>75.2016177425303</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="n">
+        <v>2168</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D648" t="n">
+        <v>37.440719876366</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="n">
+        <v>2169</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D649" t="n">
+        <v>52.8663910413483</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="n">
+        <v>2170</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D650" t="n">
+        <v>41.2866025594679</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D651" t="n">
+        <v>85.8221691879958</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="n">
+        <v>2173</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D652" t="n">
+        <v>48.2826551123359</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="n">
+        <v>2176</v>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D653" t="n">
+        <v>82.2275325353143</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="n">
+        <v>2181</v>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>CYP</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D654" t="n">
+        <v>205.753543745524</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="n">
+        <v>2182</v>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D655" t="n">
+        <v>144.011494109397</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="n">
+        <v>2183</v>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D656" t="n">
+        <v>88.7857542130501</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="n">
+        <v>2186</v>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>DNK</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D657" t="n">
+        <v>131.995824909071</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="n">
+        <v>2195</v>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D658" t="n">
+        <v>36.9831048772713</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="n">
+        <v>2198</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D659" t="n">
+        <v>78.4657338703054</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="n">
+        <v>2199</v>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D660" t="n">
+        <v>175.68711950524</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="n">
+        <v>2203</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D661" t="n">
+        <v>94.5625340522667</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="n">
+        <v>2205</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D662" t="n">
+        <v>75.9630077981996</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="n">
+        <v>2209</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D663" t="n">
+        <v>69.1989264413981</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="n">
+        <v>2217</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D664" t="n">
+        <v>108.121843229922</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="n">
+        <v>2224</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D665" t="n">
+        <v>384.881143223724</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="n">
+        <v>2227</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>HRV</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D666" t="n">
+        <v>125.410877974694</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="n">
+        <v>2229</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D667" t="n">
+        <v>185.000204092698</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>2234</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D668" t="n">
+        <v>45.4646701959453</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="n">
+        <v>2237</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D669" t="n">
+        <v>50.0752701498882</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>2239</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D670" t="n">
+        <v>237.755419559378</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>2242</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>ISL</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D671" t="n">
+        <v>93.04871996150131</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
+        <v>2243</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D672" t="n">
+        <v>60.6448526742952</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
+        <v>2244</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D673" t="n">
+        <v>72.0165023032697</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="n">
+        <v>2246</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>JOR</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D674" t="n">
+        <v>104.095459439189</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="n">
+        <v>2247</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D675" t="n">
+        <v>46.8129868368938</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="n">
+        <v>2248</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D676" t="n">
+        <v>68.3343147415612</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="n">
+        <v>2251</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>KHM</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D677" t="n">
+        <v>145.873632761406</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="n">
+        <v>2254</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D678" t="n">
+        <v>90.5851475278549</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="n">
+        <v>2257</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>LAO</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="n">
+        <v>2271</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>LTU</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D680" t="n">
+        <v>175.651612151093</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n">
+        <v>2272</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D681" t="n">
+        <v>412.177169924175</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="n">
+        <v>2273</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>LVA</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D682" t="n">
+        <v>159.892778190649</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="n">
+        <v>2276</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D683" t="n">
+        <v>100.906310201651</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>2282</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D684" t="n">
+        <v>88.7984855867186</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
+        <v>2287</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>MLT</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D685" t="n">
+        <v>245.160375092004</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n">
+        <v>2288</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>MMR</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D686" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n">
+        <v>2297</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D687" t="n">
+        <v>146.424604753908</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="n">
+        <v>2302</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D688" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="n">
+        <v>2304</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>NLD</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D689" t="n">
+        <v>184.107484252682</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="n">
+        <v>2305</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D690" t="n">
+        <v>82.6094798361389</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="n">
+        <v>2308</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D691" t="n">
+        <v>53.4761627655817</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="n">
+        <v>2312</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D692" t="n">
+        <v>33.031353478032</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="n">
+        <v>2314</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D693" t="n">
+        <v>57.2969759649721</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="n">
+        <v>2315</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D694" t="n">
+        <v>72.42968361075989</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="n">
+        <v>2318</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D695" t="n">
+        <v>123.021332860345</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="n">
+        <v>2322</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D696" t="n">
+        <v>101.364146479435</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="n">
+        <v>2329</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D697" t="n">
+        <v>93.9496509383447</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="n">
+        <v>2330</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D698" t="n">
+        <v>42.7827864294811</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="n">
+        <v>2333</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D699" t="n">
+        <v>56.8241647749332</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="n">
+        <v>2335</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D700" t="n">
+        <v>79.5998216515832</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="n">
+        <v>2336</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D701" t="n">
+        <v>332.34956775484</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="n">
+        <v>2347</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="n">
+        <v>2349</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D703" t="n">
+        <v>204.056318531151</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="n">
+        <v>2350</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>SVN</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D704" t="n">
+        <v>186.647076274632</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="n">
+        <v>2351</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D705" t="n">
+        <v>107.111751826512</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="n">
+        <v>2361</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D706" t="n">
+        <v>132.858712082871</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="n">
+        <v>2371</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D707" t="n">
+        <v>116.095794384146</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="n">
+        <v>2372</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D708" t="n">
+        <v>79.89827223143411</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="n">
+        <v>2376</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D709" t="n">
+        <v>87.3965139907244</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="n">
+        <v>2379</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D710" t="n">
+        <v>27.3139397355363</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="n">
+        <v>2385</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D711" t="n">
+        <v>183.153619147836</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="n">
+        <v>2391</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D712" t="n">
+        <v>64.94713440234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/python/output/TRADE.xlsx
+++ b/python/output/TRADE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D712"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11755,6 +11755,1262 @@
         <v>64.94713440234</v>
       </c>
     </row>
+    <row r="713">
+      <c r="A713" s="1" t="n">
+        <v>2398</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D713" t="n">
+        <v>53.033483632308</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="n">
+        <v>2402</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D714" t="n">
+        <v>199.044979237546</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="n">
+        <v>2403</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D715" t="n">
+        <v>26.6769512482215</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="n">
+        <v>2407</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D716" t="n">
+        <v>49.044339318428</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="n">
+        <v>2408</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D717" t="n">
+        <v>115.152914822732</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="n">
+        <v>2411</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D718" t="n">
+        <v>165.846946501713</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="n">
+        <v>2414</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>BGD</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D719" t="n">
+        <v>30.9829714104596</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="n">
+        <v>2415</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D720" t="n">
+        <v>119.899505956556</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="n">
+        <v>2419</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D721" t="n">
+        <v>131.584674884961</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="n">
+        <v>2423</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D722" t="n">
+        <v>33.6662298301284</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="1" t="n">
+        <v>2425</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D723" t="n">
+        <v>136.86343465048</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="n">
+        <v>2429</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D724" t="n">
+        <v>66.6323313370668</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="n">
+        <v>2431</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D725" t="n">
+        <v>135.32000224909</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="n">
+        <v>2433</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D726" t="n">
+        <v>60.7247236874408</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="n">
+        <v>2434</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D727" t="n">
+        <v>36.1051923691138</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="n">
+        <v>2435</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D728" t="n">
+        <v>48.8170039103332</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="n">
+        <v>2436</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D729" t="n">
+        <v>37.8903321242578</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="n">
+        <v>2437</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D730" t="n">
+        <v>86.74005817982891</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="n">
+        <v>2439</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D731" t="n">
+        <v>40.3881324933957</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="n">
+        <v>2442</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D732" t="n">
+        <v>72.4719990801769</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="n">
+        <v>2447</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>CYP</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D733" t="n">
+        <v>190.740788408329</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="n">
+        <v>2448</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D734" t="n">
+        <v>131.892598295876</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="n">
+        <v>2449</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D735" t="n">
+        <v>81.9625483787634</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="n">
+        <v>2452</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>DNK</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D736" t="n">
+        <v>129.625337431278</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="n">
+        <v>2461</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D737" t="n">
+        <v>40.4504007720031</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="n">
+        <v>2464</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D738" t="n">
+        <v>71.7976366055733</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="n">
+        <v>2465</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D739" t="n">
+        <v>154.592617111149</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="n">
+        <v>2469</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D740" t="n">
+        <v>85.5633906057585</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="n">
+        <v>2471</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D741" t="n">
+        <v>70.6261450610225</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="n">
+        <v>2475</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D742" t="n">
+        <v>64.9923841747803</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="n">
+        <v>2483</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D743" t="n">
+        <v>92.4710882947018</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="n">
+        <v>2490</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D744" t="n">
+        <v>353.007500147482</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="n">
+        <v>2493</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>HRV</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D745" t="n">
+        <v>107.278314008304</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="n">
+        <v>2495</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D746" t="n">
+        <v>158.385747467469</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D747" t="n">
+        <v>41.3362868707652</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="n">
+        <v>2503</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D748" t="n">
+        <v>44.9928422877561</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="n">
+        <v>2505</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D749" t="n">
+        <v>239.649627585111</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="n">
+        <v>2508</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>ISL</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D750" t="n">
+        <v>87.40494191220471</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="n">
+        <v>2509</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D751" t="n">
+        <v>57.9903207136983</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="n">
+        <v>2510</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D752" t="n">
+        <v>65.10717787631739</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="n">
+        <v>2512</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>JOR</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D753" t="n">
+        <v>100.347868752034</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="n">
+        <v>2513</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D754" t="n">
+        <v>45.1508795641248</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="n">
+        <v>2514</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D755" t="n">
+        <v>62.3342837675021</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="n">
+        <v>2517</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>KHM</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D756" t="n">
+        <v>134.206842395931</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="n">
+        <v>2520</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D757" t="n">
+        <v>82.2580090716629</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="n">
+        <v>2523</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>LAO</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D758" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="n">
+        <v>2537</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>LTU</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D759" t="n">
+        <v>149.041909014608</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="n">
+        <v>2538</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D760" t="n">
+        <v>402.566968197345</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="n">
+        <v>2539</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>LVA</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D761" t="n">
+        <v>135.642989154266</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="n">
+        <v>2542</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D762" t="n">
+        <v>93.11788441797771</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="n">
+        <v>2548</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D763" t="n">
+        <v>73.57886163652449</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="n">
+        <v>2553</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>MLT</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D764" t="n">
+        <v>221.061835472405</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="n">
+        <v>2554</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>MMR</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D765" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="1" t="n">
+        <v>2563</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D766" t="n">
+        <v>132.593461641599</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="n">
+        <v>2568</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D767" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="n">
+        <v>2570</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>NLD</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D768" t="n">
+        <v>165.030429478933</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="1" t="n">
+        <v>2571</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D769" t="n">
+        <v>80.3638456401269</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="1" t="n">
+        <v>2574</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D770" t="n">
+        <v>50.4064316790513</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="1" t="n">
+        <v>2578</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D771" t="n">
+        <v>28.4676925469837</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="1" t="n">
+        <v>2580</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D772" t="n">
+        <v>50.7851842068664</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="1" t="n">
+        <v>2581</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D773" t="n">
+        <v>67.41996931739661</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="1" t="n">
+        <v>2584</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D774" t="n">
+        <v>110.024935041815</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="1" t="n">
+        <v>2588</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D775" t="n">
+        <v>93.13585370720379</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="1" t="n">
+        <v>2595</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D776" t="n">
+        <v>83.37533240622309</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="1" t="n">
+        <v>2596</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D777" t="n">
+        <v>40.8343264105273</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="1" t="n">
+        <v>2599</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D778" t="n">
+        <v>54.1690118283683</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="1" t="n">
+        <v>2601</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D779" t="n">
+        <v>71.39302491274449</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="1" t="n">
+        <v>2602</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D780" t="n">
+        <v>325.69322405378</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="1" t="n">
+        <v>2613</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D781" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="1" t="n">
+        <v>2615</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D782" t="n">
+        <v>181.39087235645</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="1" t="n">
+        <v>2616</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>SVN</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D783" t="n">
+        <v>160.1596693009</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="1" t="n">
+        <v>2617</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D784" t="n">
+        <v>107.619709443974</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="1" t="n">
+        <v>2627</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D785" t="n">
+        <v>128.824114152375</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="1" t="n">
+        <v>2637</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D786" t="n">
+        <v>112.128858013354</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="n">
+        <v>2638</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D787" t="n">
+        <v>65.6832084738667</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>2642</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D788" t="n">
+        <v>77.5096141935657</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>2645</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D789" t="n">
+        <v>25.2903297883366</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>2651</v>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D790" t="n">
+        <v>164.818071269894</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>2657</v>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D791" t="n">
+        <v>65.6798759740707</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
